--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -83421,7 +83421,7 @@
         <v>68.2</v>
       </c>
       <c r="E4150" t="n">
-        <v>68.92</v>
+        <v>68.88</v>
       </c>
       <c r="F4150" t="n">
         <v>3679</v>
@@ -83558,13 +83558,13 @@
         <v>69.5</v>
       </c>
       <c r="D4157" t="n">
-        <v>69.18000000000001</v>
+        <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>69.44</v>
+        <v>69.23</v>
       </c>
       <c r="F4157" t="n">
-        <v>273</v>
+        <v>1576</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -83421,7 +83421,7 @@
         <v>68.2</v>
       </c>
       <c r="E4150" t="n">
-        <v>68.88</v>
+        <v>68.92</v>
       </c>
       <c r="F4150" t="n">
         <v>3679</v>
@@ -83555,16 +83555,16 @@
         <v>69.2</v>
       </c>
       <c r="C4157" t="n">
-        <v>69.5</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="D4157" t="n">
         <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>69.23</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="F4157" t="n">
-        <v>1576</v>
+        <v>5805</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4157"/>
+  <dimension ref="A1:F4158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83555,16 +83555,36 @@
         <v>69.2</v>
       </c>
       <c r="C4157" t="n">
-        <v>70.18000000000001</v>
+        <v>70.47</v>
       </c>
       <c r="D4157" t="n">
         <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>69.95999999999999</v>
+        <v>70.41</v>
       </c>
       <c r="F4157" t="n">
-        <v>5805</v>
+        <v>10087</v>
+      </c>
+    </row>
+    <row r="4158">
+      <c r="A4158" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B4158" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="C4158" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D4158" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="E4158" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="F4158" t="n">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -83521,7 +83521,7 @@
         <v>70.15000000000001</v>
       </c>
       <c r="E4155" t="n">
-        <v>70.58</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="F4155" t="n">
         <v>8722</v>
@@ -83561,7 +83561,7 @@
         <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>70.41</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F4157" t="n">
         <v>10087</v>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -83578,13 +83578,13 @@
         <v>70.40000000000001</v>
       </c>
       <c r="D4158" t="n">
-        <v>70.2</v>
+        <v>69.5</v>
       </c>
       <c r="E4158" t="n">
-        <v>70.34</v>
+        <v>69.98</v>
       </c>
       <c r="F4158" t="n">
-        <v>186</v>
+        <v>8628</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4158"/>
+  <dimension ref="A1:F4159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83561,7 +83561,7 @@
         <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>70.29000000000001</v>
+        <v>70.41</v>
       </c>
       <c r="F4157" t="n">
         <v>10087</v>
@@ -83581,10 +83581,30 @@
         <v>69.5</v>
       </c>
       <c r="E4158" t="n">
-        <v>69.98</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="F4158" t="n">
-        <v>8628</v>
+        <v>9727</v>
+      </c>
+    </row>
+    <row r="4159">
+      <c r="A4159" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B4159" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="C4159" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="D4159" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="E4159" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="F4159" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4159"/>
+  <dimension ref="A1:F4160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83561,7 +83561,7 @@
         <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>70.41</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F4157" t="n">
         <v>10087</v>
@@ -83595,16 +83595,36 @@
         <v>69.98999999999999</v>
       </c>
       <c r="C4159" t="n">
-        <v>69.98999999999999</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="D4159" t="n">
-        <v>69.81</v>
+        <v>69.5</v>
       </c>
       <c r="E4159" t="n">
-        <v>69.90000000000001</v>
+        <v>69.78</v>
       </c>
       <c r="F4159" t="n">
-        <v>40</v>
+        <v>5238</v>
+      </c>
+    </row>
+    <row r="4160">
+      <c r="A4160" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B4160" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="C4160" t="n">
+        <v>69.67</v>
+      </c>
+      <c r="D4160" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="E4160" t="n">
+        <v>69.61</v>
+      </c>
+      <c r="F4160" t="n">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4160"/>
+  <dimension ref="A1:F4161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83561,7 +83561,7 @@
         <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>70.29000000000001</v>
+        <v>70.41</v>
       </c>
       <c r="F4157" t="n">
         <v>10087</v>
@@ -83618,13 +83618,33 @@
         <v>69.67</v>
       </c>
       <c r="D4160" t="n">
-        <v>69.51000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E4160" t="n">
-        <v>69.61</v>
+        <v>69.25</v>
       </c>
       <c r="F4160" t="n">
-        <v>222</v>
+        <v>5846</v>
+      </c>
+    </row>
+    <row r="4161">
+      <c r="A4161" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B4161" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="C4161" t="n">
+        <v>69.36</v>
+      </c>
+      <c r="D4161" t="n">
+        <v>69.18000000000001</v>
+      </c>
+      <c r="E4161" t="n">
+        <v>69.34</v>
+      </c>
+      <c r="F4161" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4161"/>
+  <dimension ref="A1:F4162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83561,7 +83561,7 @@
         <v>69.03</v>
       </c>
       <c r="E4157" t="n">
-        <v>70.41</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F4157" t="n">
         <v>10087</v>
@@ -83638,13 +83638,33 @@
         <v>69.36</v>
       </c>
       <c r="D4161" t="n">
-        <v>69.18000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="E4161" t="n">
-        <v>69.34</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="F4161" t="n">
-        <v>93</v>
+        <v>7788</v>
+      </c>
+    </row>
+    <row r="4162">
+      <c r="A4162" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B4162" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="C4162" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="D4162" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="E4162" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="F4162" t="n">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4162"/>
+  <dimension ref="A1:F4163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83658,13 +83658,33 @@
         <v>68.90000000000001</v>
       </c>
       <c r="D4162" t="n">
-        <v>68.73</v>
+        <v>68.3</v>
       </c>
       <c r="E4162" t="n">
-        <v>68.8</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="F4162" t="n">
-        <v>244</v>
+        <v>7333</v>
+      </c>
+    </row>
+    <row r="4163">
+      <c r="A4163" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B4163" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="C4163" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="D4163" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="E4163" t="n">
+        <v>68.69</v>
+      </c>
+      <c r="F4163" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4163"/>
+  <dimension ref="A1:F4164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83678,13 +83678,33 @@
         <v>68.7</v>
       </c>
       <c r="D4163" t="n">
-        <v>68.59999999999999</v>
+        <v>68.14</v>
       </c>
       <c r="E4163" t="n">
-        <v>68.69</v>
+        <v>68.3</v>
       </c>
       <c r="F4163" t="n">
-        <v>120</v>
+        <v>5698</v>
+      </c>
+    </row>
+    <row r="4164">
+      <c r="A4164" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B4164" t="n">
+        <v>68.36</v>
+      </c>
+      <c r="C4164" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="D4164" t="n">
+        <v>68.31</v>
+      </c>
+      <c r="E4164" t="n">
+        <v>68.31999999999999</v>
+      </c>
+      <c r="F4164" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4164"/>
+  <dimension ref="A1:F4165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83695,16 +83695,36 @@
         <v>68.36</v>
       </c>
       <c r="C4164" t="n">
-        <v>68.39</v>
+        <v>68.48</v>
       </c>
       <c r="D4164" t="n">
-        <v>68.31</v>
+        <v>67.83</v>
       </c>
       <c r="E4164" t="n">
-        <v>68.31999999999999</v>
+        <v>68.42</v>
       </c>
       <c r="F4164" t="n">
-        <v>44</v>
+        <v>9513</v>
+      </c>
+    </row>
+    <row r="4165">
+      <c r="A4165" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B4165" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="C4165" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="D4165" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="E4165" t="n">
+        <v>68.41</v>
+      </c>
+      <c r="F4165" t="n">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4165"/>
+  <dimension ref="A1:F4166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83715,16 +83715,36 @@
         <v>68.37</v>
       </c>
       <c r="C4165" t="n">
-        <v>68.5</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="D4165" t="n">
         <v>68.37</v>
       </c>
       <c r="E4165" t="n">
-        <v>68.41</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="F4165" t="n">
-        <v>168</v>
+        <v>6583</v>
+      </c>
+    </row>
+    <row r="4166">
+      <c r="A4166" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B4166" t="n">
+        <v>68.88</v>
+      </c>
+      <c r="C4166" t="n">
+        <v>69.04000000000001</v>
+      </c>
+      <c r="D4166" t="n">
+        <v>68.73999999999999</v>
+      </c>
+      <c r="E4166" t="n">
+        <v>68.86</v>
+      </c>
+      <c r="F4166" t="n">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4166"/>
+  <dimension ref="A1:F4167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83661,7 +83661,7 @@
         <v>68.3</v>
       </c>
       <c r="E4162" t="n">
-        <v>68.65000000000001</v>
+        <v>68.56999999999999</v>
       </c>
       <c r="F4162" t="n">
         <v>7333</v>
@@ -83681,7 +83681,7 @@
         <v>68.14</v>
       </c>
       <c r="E4163" t="n">
-        <v>68.3</v>
+        <v>68.33</v>
       </c>
       <c r="F4163" t="n">
         <v>5698</v>
@@ -83735,16 +83735,36 @@
         <v>68.88</v>
       </c>
       <c r="C4166" t="n">
-        <v>69.04000000000001</v>
+        <v>70</v>
       </c>
       <c r="D4166" t="n">
         <v>68.73999999999999</v>
       </c>
       <c r="E4166" t="n">
-        <v>68.86</v>
+        <v>69.89</v>
       </c>
       <c r="F4166" t="n">
-        <v>161</v>
+        <v>8370</v>
+      </c>
+    </row>
+    <row r="4167">
+      <c r="A4167" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B4167" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="C4167" t="n">
+        <v>70.05</v>
+      </c>
+      <c r="D4167" t="n">
+        <v>69.89</v>
+      </c>
+      <c r="E4167" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4167" t="n">
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4167"/>
+  <dimension ref="A1:F4168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83701,7 +83701,7 @@
         <v>67.83</v>
       </c>
       <c r="E4164" t="n">
-        <v>68.42</v>
+        <v>68.37</v>
       </c>
       <c r="F4164" t="n">
         <v>9513</v>
@@ -83755,16 +83755,36 @@
         <v>69.90000000000001</v>
       </c>
       <c r="C4167" t="n">
-        <v>70.05</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="D4167" t="n">
-        <v>69.89</v>
+        <v>69.56</v>
       </c>
       <c r="E4167" t="n">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="F4167" t="n">
-        <v>215</v>
+        <v>5551</v>
+      </c>
+    </row>
+    <row r="4168">
+      <c r="A4168" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B4168" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="C4168" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="D4168" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="E4168" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="F4168" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4168"/>
+  <dimension ref="A1:F4169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83761,7 +83761,7 @@
         <v>69.56</v>
       </c>
       <c r="E4167" t="n">
-        <v>69.8</v>
+        <v>69.81</v>
       </c>
       <c r="F4167" t="n">
         <v>5551</v>
@@ -83775,16 +83775,36 @@
         <v>69.8</v>
       </c>
       <c r="C4168" t="n">
-        <v>69.81</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="D4168" t="n">
         <v>69.8</v>
       </c>
       <c r="E4168" t="n">
-        <v>69.8</v>
+        <v>70.34</v>
       </c>
       <c r="F4168" t="n">
-        <v>22</v>
+        <v>10956</v>
+      </c>
+    </row>
+    <row r="4169">
+      <c r="A4169" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B4169" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="C4169" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="D4169" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="E4169" t="n">
+        <v>70.20999999999999</v>
+      </c>
+      <c r="F4169" t="n">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4169"/>
+  <dimension ref="A1:F4170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83761,7 +83761,7 @@
         <v>69.56</v>
       </c>
       <c r="E4167" t="n">
-        <v>69.81</v>
+        <v>69.8</v>
       </c>
       <c r="F4167" t="n">
         <v>5551</v>
@@ -83795,16 +83795,36 @@
         <v>70.34</v>
       </c>
       <c r="C4169" t="n">
-        <v>70.34</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="D4169" t="n">
-        <v>70.11</v>
+        <v>69.34</v>
       </c>
       <c r="E4169" t="n">
-        <v>70.20999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F4169" t="n">
-        <v>194</v>
+        <v>8165</v>
+      </c>
+    </row>
+    <row r="4170">
+      <c r="A4170" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B4170" t="n">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="C4170" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="D4170" t="n">
+        <v>69.26000000000001</v>
+      </c>
+      <c r="E4170" t="n">
+        <v>69.34</v>
+      </c>
+      <c r="F4170" t="n">
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4170"/>
+  <dimension ref="A1:F4171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83761,7 +83761,7 @@
         <v>69.56</v>
       </c>
       <c r="E4167" t="n">
-        <v>69.8</v>
+        <v>69.81</v>
       </c>
       <c r="F4167" t="n">
         <v>5551</v>
@@ -83781,7 +83781,7 @@
         <v>69.8</v>
       </c>
       <c r="E4168" t="n">
-        <v>70.34</v>
+        <v>70.33</v>
       </c>
       <c r="F4168" t="n">
         <v>10956</v>
@@ -83815,16 +83815,36 @@
         <v>69.26000000000001</v>
       </c>
       <c r="C4170" t="n">
-        <v>69.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="D4170" t="n">
-        <v>69.26000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="E4170" t="n">
-        <v>69.34</v>
+        <v>70.22</v>
       </c>
       <c r="F4170" t="n">
-        <v>246</v>
+        <v>6575</v>
+      </c>
+    </row>
+    <row r="4171">
+      <c r="A4171" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B4171" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="C4171" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="D4171" t="n">
+        <v>70.22</v>
+      </c>
+      <c r="E4171" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="F4171" t="n">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4171"/>
+  <dimension ref="A1:F4172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83835,16 +83835,36 @@
         <v>70.22</v>
       </c>
       <c r="C4171" t="n">
-        <v>70.43000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="D4171" t="n">
-        <v>70.22</v>
+        <v>69.92</v>
       </c>
       <c r="E4171" t="n">
-        <v>70.36</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F4171" t="n">
-        <v>90</v>
+        <v>4687</v>
+      </c>
+    </row>
+    <row r="4172">
+      <c r="A4172" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B4172" t="n">
+        <v>70.63</v>
+      </c>
+      <c r="C4172" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="D4172" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="E4172" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="F4172" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4172"/>
+  <dimension ref="A1:F4173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83701,7 +83701,7 @@
         <v>67.83</v>
       </c>
       <c r="E4164" t="n">
-        <v>68.37</v>
+        <v>68.42</v>
       </c>
       <c r="F4164" t="n">
         <v>9513</v>
@@ -83761,7 +83761,7 @@
         <v>69.56</v>
       </c>
       <c r="E4167" t="n">
-        <v>69.81</v>
+        <v>69.8</v>
       </c>
       <c r="F4167" t="n">
         <v>5551</v>
@@ -83781,7 +83781,7 @@
         <v>69.8</v>
       </c>
       <c r="E4168" t="n">
-        <v>70.33</v>
+        <v>70.34</v>
       </c>
       <c r="F4168" t="n">
         <v>10956</v>
@@ -83855,16 +83855,36 @@
         <v>70.63</v>
       </c>
       <c r="C4172" t="n">
-        <v>70.7</v>
+        <v>71.88</v>
       </c>
       <c r="D4172" t="n">
         <v>70.55</v>
       </c>
       <c r="E4172" t="n">
-        <v>70.59999999999999</v>
+        <v>71.62</v>
       </c>
       <c r="F4172" t="n">
-        <v>68</v>
+        <v>9554</v>
+      </c>
+    </row>
+    <row r="4173">
+      <c r="A4173" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B4173" t="n">
+        <v>71.62</v>
+      </c>
+      <c r="C4173" t="n">
+        <v>71.81999999999999</v>
+      </c>
+      <c r="D4173" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="E4173" t="n">
+        <v>71.73999999999999</v>
+      </c>
+      <c r="F4173" t="n">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4173"/>
+  <dimension ref="A1:F4174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83878,13 +83878,33 @@
         <v>71.81999999999999</v>
       </c>
       <c r="D4173" t="n">
-        <v>71.55</v>
+        <v>70.81</v>
       </c>
       <c r="E4173" t="n">
-        <v>71.73999999999999</v>
+        <v>70.97</v>
       </c>
       <c r="F4173" t="n">
-        <v>272</v>
+        <v>8352</v>
+      </c>
+    </row>
+    <row r="4174">
+      <c r="A4174" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B4174" t="n">
+        <v>70.97</v>
+      </c>
+      <c r="C4174" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="D4174" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E4174" t="n">
+        <v>71</v>
+      </c>
+      <c r="F4174" t="n">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4174"/>
+  <dimension ref="A1:F4175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83701,7 +83701,7 @@
         <v>67.83</v>
       </c>
       <c r="E4164" t="n">
-        <v>68.42</v>
+        <v>68.37</v>
       </c>
       <c r="F4164" t="n">
         <v>9513</v>
@@ -83895,16 +83895,36 @@
         <v>70.97</v>
       </c>
       <c r="C4174" t="n">
-        <v>71.01000000000001</v>
+        <v>71.87</v>
       </c>
       <c r="D4174" t="n">
         <v>70.8</v>
       </c>
       <c r="E4174" t="n">
-        <v>71</v>
+        <v>71.34</v>
       </c>
       <c r="F4174" t="n">
-        <v>169</v>
+        <v>6376</v>
+      </c>
+    </row>
+    <row r="4175">
+      <c r="A4175" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B4175" t="n">
+        <v>71.34</v>
+      </c>
+      <c r="C4175" t="n">
+        <v>71.38</v>
+      </c>
+      <c r="D4175" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="E4175" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F4175" t="n">
+        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4175"/>
+  <dimension ref="A1:F4176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83761,7 +83761,7 @@
         <v>69.56</v>
       </c>
       <c r="E4167" t="n">
-        <v>69.8</v>
+        <v>69.81</v>
       </c>
       <c r="F4167" t="n">
         <v>5551</v>
@@ -83781,7 +83781,7 @@
         <v>69.8</v>
       </c>
       <c r="E4168" t="n">
-        <v>70.34</v>
+        <v>70.33</v>
       </c>
       <c r="F4168" t="n">
         <v>10956</v>
@@ -83915,16 +83915,36 @@
         <v>71.34</v>
       </c>
       <c r="C4175" t="n">
-        <v>71.38</v>
+        <v>71.48</v>
       </c>
       <c r="D4175" t="n">
-        <v>71.2</v>
+        <v>70.52</v>
       </c>
       <c r="E4175" t="n">
-        <v>71.3</v>
+        <v>71.27</v>
       </c>
       <c r="F4175" t="n">
-        <v>703</v>
+        <v>12284</v>
+      </c>
+    </row>
+    <row r="4176">
+      <c r="A4176" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B4176" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="C4176" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="D4176" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="E4176" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="F4176" t="n">
+        <v>750</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4176"/>
+  <dimension ref="A1:F4177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83935,16 +83935,36 @@
         <v>71.34999999999999</v>
       </c>
       <c r="C4176" t="n">
-        <v>71.7</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="D4176" t="n">
         <v>71.33</v>
       </c>
       <c r="E4176" t="n">
-        <v>71.55</v>
+        <v>71.88</v>
       </c>
       <c r="F4176" t="n">
-        <v>750</v>
+        <v>8927</v>
+      </c>
+    </row>
+    <row r="4177">
+      <c r="A4177" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B4177" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="C4177" t="n">
+        <v>72.09</v>
+      </c>
+      <c r="D4177" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="E4177" t="n">
+        <v>72.08</v>
+      </c>
+      <c r="F4177" t="n">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4177"/>
+  <dimension ref="A1:F4178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83955,16 +83955,36 @@
         <v>71.95</v>
       </c>
       <c r="C4177" t="n">
-        <v>72.09</v>
+        <v>72.12</v>
       </c>
       <c r="D4177" t="n">
-        <v>71.84</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="E4177" t="n">
-        <v>72.08</v>
+        <v>71.7</v>
       </c>
       <c r="F4177" t="n">
-        <v>71</v>
+        <v>11192</v>
+      </c>
+    </row>
+    <row r="4178">
+      <c r="A4178" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B4178" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="C4178" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="D4178" t="n">
+        <v>71.59</v>
+      </c>
+      <c r="E4178" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="F4178" t="n">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4178"/>
+  <dimension ref="A1:F4179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83941,7 +83941,7 @@
         <v>71.33</v>
       </c>
       <c r="E4176" t="n">
-        <v>71.88</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F4176" t="n">
         <v>8927</v>
@@ -83975,16 +83975,36 @@
         <v>71.59</v>
       </c>
       <c r="C4178" t="n">
-        <v>71.75</v>
+        <v>72.25</v>
       </c>
       <c r="D4178" t="n">
-        <v>71.59</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E4178" t="n">
-        <v>71.66</v>
+        <v>72</v>
       </c>
       <c r="F4178" t="n">
-        <v>124</v>
+        <v>5975</v>
+      </c>
+    </row>
+    <row r="4179">
+      <c r="A4179" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B4179" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="C4179" t="n">
+        <v>72.23</v>
+      </c>
+      <c r="D4179" t="n">
+        <v>72.03</v>
+      </c>
+      <c r="E4179" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="F4179" t="n">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4179"/>
+  <dimension ref="A1:F4180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83941,7 +83941,7 @@
         <v>71.33</v>
       </c>
       <c r="E4176" t="n">
-        <v>71.79000000000001</v>
+        <v>71.88</v>
       </c>
       <c r="F4176" t="n">
         <v>8927</v>
@@ -83995,16 +83995,36 @@
         <v>72.2</v>
       </c>
       <c r="C4179" t="n">
-        <v>72.23</v>
+        <v>72.25</v>
       </c>
       <c r="D4179" t="n">
-        <v>72.03</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="E4179" t="n">
-        <v>72.18000000000001</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="F4179" t="n">
-        <v>145</v>
+        <v>8238</v>
+      </c>
+    </row>
+    <row r="4180">
+      <c r="A4180" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B4180" t="n">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="C4180" t="n">
+        <v>71.23999999999999</v>
+      </c>
+      <c r="D4180" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="E4180" t="n">
+        <v>71.06999999999999</v>
+      </c>
+      <c r="F4180" t="n">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -83941,7 +83941,7 @@
         <v>71.33</v>
       </c>
       <c r="E4176" t="n">
-        <v>71.88</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F4176" t="n">
         <v>8927</v>
@@ -84015,16 +84015,16 @@
         <v>71.23999999999999</v>
       </c>
       <c r="C4180" t="n">
-        <v>71.23999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="D4180" t="n">
         <v>71.01000000000001</v>
       </c>
       <c r="E4180" t="n">
-        <v>71.06999999999999</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="F4180" t="n">
-        <v>212</v>
+        <v>3747</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4180"/>
+  <dimension ref="A1:F4181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84021,10 +84021,30 @@
         <v>71.01000000000001</v>
       </c>
       <c r="E4180" t="n">
-        <v>71.51000000000001</v>
+        <v>71.38</v>
       </c>
       <c r="F4180" t="n">
-        <v>3747</v>
+        <v>4660</v>
+      </c>
+    </row>
+    <row r="4181">
+      <c r="A4181" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B4181" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="C4181" t="n">
+        <v>71.69</v>
+      </c>
+      <c r="D4181" t="n">
+        <v>71.44</v>
+      </c>
+      <c r="E4181" t="n">
+        <v>71.53</v>
+      </c>
+      <c r="F4181" t="n">
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -83941,7 +83941,7 @@
         <v>71.33</v>
       </c>
       <c r="E4176" t="n">
-        <v>71.79000000000001</v>
+        <v>71.88</v>
       </c>
       <c r="F4176" t="n">
         <v>8927</v>
@@ -84044,7 +84044,7 @@
         <v>71.53</v>
       </c>
       <c r="F4181" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4181"/>
+  <dimension ref="A1:F4183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83941,7 +83941,7 @@
         <v>71.33</v>
       </c>
       <c r="E4176" t="n">
-        <v>71.88</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F4176" t="n">
         <v>8927</v>
@@ -83981,7 +83981,7 @@
         <v>71.34999999999999</v>
       </c>
       <c r="E4178" t="n">
-        <v>72</v>
+        <v>72.02</v>
       </c>
       <c r="F4178" t="n">
         <v>5975</v>
@@ -84038,13 +84038,53 @@
         <v>71.69</v>
       </c>
       <c r="D4181" t="n">
-        <v>71.44</v>
+        <v>71</v>
       </c>
       <c r="E4181" t="n">
-        <v>71.53</v>
+        <v>71.06</v>
       </c>
       <c r="F4181" t="n">
-        <v>85</v>
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="4182">
+      <c r="A4182" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B4182" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="C4182" t="n">
+        <v>72.28</v>
+      </c>
+      <c r="D4182" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="E4182" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="F4182" t="n">
+        <v>5246</v>
+      </c>
+    </row>
+    <row r="4183">
+      <c r="A4183" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B4183" t="n">
+        <v>72.23999999999999</v>
+      </c>
+      <c r="C4183" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="D4183" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="E4183" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="F4183" t="n">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4183"/>
+  <dimension ref="A1:F4184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84041,7 +84041,7 @@
         <v>71</v>
       </c>
       <c r="E4181" t="n">
-        <v>71.06</v>
+        <v>71.05</v>
       </c>
       <c r="F4181" t="n">
         <v>3783</v>
@@ -84075,16 +84075,36 @@
         <v>72.23999999999999</v>
       </c>
       <c r="C4183" t="n">
-        <v>72.26000000000001</v>
+        <v>72.69</v>
       </c>
       <c r="D4183" t="n">
-        <v>72.18000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="E4183" t="n">
-        <v>72.2</v>
+        <v>72.61</v>
       </c>
       <c r="F4183" t="n">
-        <v>178</v>
+        <v>3989</v>
+      </c>
+    </row>
+    <row r="4184">
+      <c r="A4184" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B4184" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="C4184" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="D4184" t="n">
+        <v>72.43000000000001</v>
+      </c>
+      <c r="E4184" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="F4184" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4184"/>
+  <dimension ref="A1:F4185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84098,13 +84098,33 @@
         <v>72.63</v>
       </c>
       <c r="D4184" t="n">
-        <v>72.43000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E4184" t="n">
-        <v>72.63</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="F4184" t="n">
-        <v>44</v>
+        <v>4893</v>
+      </c>
+    </row>
+    <row r="4185">
+      <c r="A4185" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B4185" t="n">
+        <v>72</v>
+      </c>
+      <c r="C4185" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="D4185" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="E4185" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="F4185" t="n">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4185"/>
+  <dimension ref="A1:F4186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84115,16 +84115,36 @@
         <v>72</v>
       </c>
       <c r="C4185" t="n">
-        <v>72.05</v>
+        <v>72.19</v>
       </c>
       <c r="D4185" t="n">
-        <v>71.95</v>
+        <v>71.7</v>
       </c>
       <c r="E4185" t="n">
-        <v>72.05</v>
+        <v>71.72</v>
       </c>
       <c r="F4185" t="n">
-        <v>144</v>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="4186">
+      <c r="A4186" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B4186" t="n">
+        <v>71.77</v>
+      </c>
+      <c r="C4186" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="D4186" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="E4186" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="F4186" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -84041,7 +84041,7 @@
         <v>71</v>
       </c>
       <c r="E4181" t="n">
-        <v>71.05</v>
+        <v>71.06</v>
       </c>
       <c r="F4181" t="n">
         <v>3783</v>
@@ -84101,7 +84101,7 @@
         <v>71.8</v>
       </c>
       <c r="E4184" t="n">
-        <v>71.84999999999999</v>
+        <v>71.88</v>
       </c>
       <c r="F4184" t="n">
         <v>4893</v>
@@ -84121,7 +84121,7 @@
         <v>71.7</v>
       </c>
       <c r="E4185" t="n">
-        <v>71.72</v>
+        <v>71.75</v>
       </c>
       <c r="F4185" t="n">
         <v>2485</v>
@@ -84144,7 +84144,7 @@
         <v>71.66</v>
       </c>
       <c r="F4186" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4186"/>
+  <dimension ref="A1:F4187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84041,7 +84041,7 @@
         <v>71</v>
       </c>
       <c r="E4181" t="n">
-        <v>71.06</v>
+        <v>71.05</v>
       </c>
       <c r="F4181" t="n">
         <v>3783</v>
@@ -84101,7 +84101,7 @@
         <v>71.8</v>
       </c>
       <c r="E4184" t="n">
-        <v>71.88</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="F4184" t="n">
         <v>4893</v>
@@ -84121,7 +84121,7 @@
         <v>71.7</v>
       </c>
       <c r="E4185" t="n">
-        <v>71.75</v>
+        <v>71.72</v>
       </c>
       <c r="F4185" t="n">
         <v>2485</v>
@@ -84138,13 +84138,33 @@
         <v>71.79000000000001</v>
       </c>
       <c r="D4186" t="n">
-        <v>71.66</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="E4186" t="n">
-        <v>71.66</v>
+        <v>71.08</v>
       </c>
       <c r="F4186" t="n">
-        <v>48</v>
+        <v>3785</v>
+      </c>
+    </row>
+    <row r="4187">
+      <c r="A4187" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B4187" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="C4187" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D4187" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="E4187" t="n">
+        <v>71.19</v>
+      </c>
+      <c r="F4187" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4187"/>
+  <dimension ref="A1:F4188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84041,7 +84041,7 @@
         <v>71</v>
       </c>
       <c r="E4181" t="n">
-        <v>71.05</v>
+        <v>71.06</v>
       </c>
       <c r="F4181" t="n">
         <v>3783</v>
@@ -84101,7 +84101,7 @@
         <v>71.8</v>
       </c>
       <c r="E4184" t="n">
-        <v>71.84999999999999</v>
+        <v>71.88</v>
       </c>
       <c r="F4184" t="n">
         <v>4893</v>
@@ -84121,7 +84121,7 @@
         <v>71.7</v>
       </c>
       <c r="E4185" t="n">
-        <v>71.72</v>
+        <v>71.75</v>
       </c>
       <c r="F4185" t="n">
         <v>2485</v>
@@ -84155,16 +84155,36 @@
         <v>71.19</v>
       </c>
       <c r="C4187" t="n">
-        <v>71.3</v>
+        <v>71.33</v>
       </c>
       <c r="D4187" t="n">
-        <v>71.19</v>
+        <v>70.84</v>
       </c>
       <c r="E4187" t="n">
-        <v>71.19</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="F4187" t="n">
-        <v>23</v>
+        <v>5824</v>
+      </c>
+    </row>
+    <row r="4188">
+      <c r="A4188" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B4188" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="C4188" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="D4188" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="E4188" t="n">
+        <v>70.95999999999999</v>
+      </c>
+      <c r="F4188" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4188"/>
+  <dimension ref="A1:F4189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84178,13 +84178,33 @@
         <v>71.01000000000001</v>
       </c>
       <c r="D4188" t="n">
-        <v>70.95999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E4188" t="n">
-        <v>70.95999999999999</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="F4188" t="n">
-        <v>30</v>
+        <v>3662</v>
+      </c>
+    </row>
+    <row r="4189">
+      <c r="A4189" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B4189" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="C4189" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="D4189" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E4189" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="F4189" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/database/CCM1!.xlsx
+++ b/database/CCM1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4189"/>
+  <dimension ref="A1:F4190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84161,7 +84161,7 @@
         <v>70.84</v>
       </c>
       <c r="E4187" t="n">
-        <v>71.04000000000001</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="F4187" t="n">
         <v>5824</v>
@@ -84198,13 +84198,33 @@
         <v>70.87</v>
       </c>
       <c r="D4189" t="n">
-        <v>70.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E4189" t="n">
-        <v>70.81999999999999</v>
+        <v>69.92</v>
       </c>
       <c r="F4189" t="n">
-        <v>63</v>
+        <v>8190</v>
+      </c>
+    </row>
+    <row r="4190">
+      <c r="A4190" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B4190" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="C4190" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="D4190" t="n">
+        <v>69.78</v>
+      </c>
+      <c r="E4190" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="F4190" t="n">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
